--- a/output/laminas_comunales/comunal_o_ocup_a_2020_magallanes.xlsx
+++ b/output/laminas_comunales/comunal_o_ocup_a_2020_magallanes.xlsx
@@ -352,7 +352,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C6"/>
+  <dimension ref="A1:C36"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -384,67 +384,517 @@
         </is>
       </c>
       <c r="C2">
-        <v>47.0992576299148</v>
+        <v>64.5752895752896</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>12302</t>
+          <t>12101</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Primavera</t>
+          <t>Punta Arenas</t>
         </is>
       </c>
       <c r="C3">
-        <v>42.8780487804878</v>
+        <v>60.6461531913988</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>12101</t>
+          <t>12302</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Punta Arenas</t>
+          <t>Primavera</t>
         </is>
       </c>
       <c r="C4">
-        <v>41.6234693110961</v>
+        <v>60.0518806744488</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>12401</t>
+          <t>12302</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Natales</t>
+          <t>Primavera</t>
         </is>
       </c>
       <c r="C5">
-        <v>39.0625</v>
+        <v>57.7235772357724</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>12301</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Porvenir</t>
+        </is>
+      </c>
+      <c r="C6">
+        <v>57.1746530505368</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>12401</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Natales</t>
+        </is>
+      </c>
+      <c r="C7">
+        <v>55.997534361557</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>12101</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Punta Arenas</t>
+        </is>
+      </c>
+      <c r="C8">
+        <v>55.7033575762143</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>12302</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Primavera</t>
+        </is>
+      </c>
+      <c r="C9">
+        <v>49.3939393939394</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>12301</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Porvenir</t>
+        </is>
+      </c>
+      <c r="C10">
+        <v>48.8397668536237</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
           <t>12201</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B11" t="inlineStr">
         <is>
           <t>Cabo de Hornos</t>
         </is>
       </c>
-      <c r="C6">
+      <c r="C11">
+        <v>48.6969696969697</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>12301</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Porvenir</t>
+        </is>
+      </c>
+      <c r="C12">
+        <v>47.0992576299148</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>12401</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Natales</t>
+        </is>
+      </c>
+      <c r="C13">
+        <v>47.0944648157849</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>12101</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Punta Arenas</t>
+        </is>
+      </c>
+      <c r="C14">
+        <v>45.6659927021819</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>12301</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Porvenir</t>
+        </is>
+      </c>
+      <c r="C15">
+        <v>44.9233518938613</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>12301</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Porvenir</t>
+        </is>
+      </c>
+      <c r="C16">
+        <v>43.8185443668993</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>12401</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Natales</t>
+        </is>
+      </c>
+      <c r="C17">
+        <v>43.5056660446912</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>12302</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Primavera</t>
+        </is>
+      </c>
+      <c r="C18">
+        <v>42.8780487804878</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>12201</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Cabo de Hornos</t>
+        </is>
+      </c>
+      <c r="C19">
+        <v>42.1129503407984</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>12101</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Punta Arenas</t>
+        </is>
+      </c>
+      <c r="C20">
+        <v>41.6234693110961</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>12401</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Natales</t>
+        </is>
+      </c>
+      <c r="C21">
+        <v>39.0625</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>12401</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Natales</t>
+        </is>
+      </c>
+      <c r="C22">
+        <v>38.0168280104949</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>12201</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Cabo de Hornos</t>
+        </is>
+      </c>
+      <c r="C23">
+        <v>37.9723919438787</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>12101</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Punta Arenas</t>
+        </is>
+      </c>
+      <c r="C24">
+        <v>37.6428162129292</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>12201</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Cabo de Hornos</t>
+        </is>
+      </c>
+      <c r="C25">
         <v>36.7715617715618</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>12201</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Cabo de Hornos</t>
+        </is>
+      </c>
+      <c r="C26">
+        <v>35.4962749339101</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>12302</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Primavera</t>
+        </is>
+      </c>
+      <c r="C27">
+        <v>35.3333333333333</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>12401</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Natales</t>
+        </is>
+      </c>
+      <c r="C28">
+        <v>34.4631836811608</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>12101</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Punta Arenas</t>
+        </is>
+      </c>
+      <c r="C29">
+        <v>33.9116318301039</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>12201</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Cabo de Hornos</t>
+        </is>
+      </c>
+      <c r="C30">
+        <v>29.3172690763052</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>12302</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Primavera</t>
+        </is>
+      </c>
+      <c r="C31">
+        <v>29.1666666666667</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>12201</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Cabo de Hornos</t>
+        </is>
+      </c>
+      <c r="C32">
+        <v>20.6736353077816</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>12302</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Primavera</t>
+        </is>
+      </c>
+      <c r="C33">
+        <v>19.7586726998492</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>12301</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Porvenir</t>
+        </is>
+      </c>
+      <c r="C34">
+        <v>15.9178529062871</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>12101</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Punta Arenas</t>
+        </is>
+      </c>
+      <c r="C35">
+        <v>13.3539550106892</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>12401</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Natales</t>
+        </is>
+      </c>
+      <c r="C36">
+        <v>10.7304090020888</v>
       </c>
     </row>
   </sheetData>

--- a/output/laminas_comunales/comunal_o_ocup_a_2020_magallanes.xlsx
+++ b/output/laminas_comunales/comunal_o_ocup_a_2020_magallanes.xlsx
@@ -352,7 +352,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C36"/>
+  <dimension ref="A1:C6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -384,517 +384,67 @@
         </is>
       </c>
       <c r="C2">
-        <v>64.5752895752896</v>
+        <v>47.0992576299148</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>12101</t>
+          <t>12302</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Punta Arenas</t>
+          <t>Primavera</t>
         </is>
       </c>
       <c r="C3">
-        <v>60.6461531913988</v>
+        <v>42.8780487804878</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>12302</t>
+          <t>12101</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Primavera</t>
+          <t>Punta Arenas</t>
         </is>
       </c>
       <c r="C4">
-        <v>60.0518806744488</v>
+        <v>41.6234693110961</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>12302</t>
+          <t>12401</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Primavera</t>
+          <t>Natales</t>
         </is>
       </c>
       <c r="C5">
-        <v>57.7235772357724</v>
+        <v>39.0625</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>12301</t>
+          <t>12201</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Porvenir</t>
+          <t>Cabo de Hornos</t>
         </is>
       </c>
       <c r="C6">
-        <v>57.1746530505368</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>12401</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Natales</t>
-        </is>
-      </c>
-      <c r="C7">
-        <v>55.997534361557</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>12101</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Punta Arenas</t>
-        </is>
-      </c>
-      <c r="C8">
-        <v>55.7033575762143</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>12302</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Primavera</t>
-        </is>
-      </c>
-      <c r="C9">
-        <v>49.3939393939394</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>12301</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>Porvenir</t>
-        </is>
-      </c>
-      <c r="C10">
-        <v>48.8397668536237</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>12201</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Cabo de Hornos</t>
-        </is>
-      </c>
-      <c r="C11">
-        <v>48.6969696969697</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>12301</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Porvenir</t>
-        </is>
-      </c>
-      <c r="C12">
-        <v>47.0992576299148</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>12401</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>Natales</t>
-        </is>
-      </c>
-      <c r="C13">
-        <v>47.0944648157849</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>12101</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>Punta Arenas</t>
-        </is>
-      </c>
-      <c r="C14">
-        <v>45.6659927021819</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>12301</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>Porvenir</t>
-        </is>
-      </c>
-      <c r="C15">
-        <v>44.9233518938613</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>12301</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>Porvenir</t>
-        </is>
-      </c>
-      <c r="C16">
-        <v>43.8185443668993</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>12401</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>Natales</t>
-        </is>
-      </c>
-      <c r="C17">
-        <v>43.5056660446912</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>12302</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>Primavera</t>
-        </is>
-      </c>
-      <c r="C18">
-        <v>42.8780487804878</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>12201</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>Cabo de Hornos</t>
-        </is>
-      </c>
-      <c r="C19">
-        <v>42.1129503407984</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>12101</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>Punta Arenas</t>
-        </is>
-      </c>
-      <c r="C20">
-        <v>41.6234693110961</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>12401</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>Natales</t>
-        </is>
-      </c>
-      <c r="C21">
-        <v>39.0625</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>12401</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>Natales</t>
-        </is>
-      </c>
-      <c r="C22">
-        <v>38.0168280104949</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>12201</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>Cabo de Hornos</t>
-        </is>
-      </c>
-      <c r="C23">
-        <v>37.9723919438787</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>12101</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>Punta Arenas</t>
-        </is>
-      </c>
-      <c r="C24">
-        <v>37.6428162129292</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>12201</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>Cabo de Hornos</t>
-        </is>
-      </c>
-      <c r="C25">
         <v>36.7715617715618</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>12201</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>Cabo de Hornos</t>
-        </is>
-      </c>
-      <c r="C26">
-        <v>35.4962749339101</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>12302</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>Primavera</t>
-        </is>
-      </c>
-      <c r="C27">
-        <v>35.3333333333333</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>12401</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>Natales</t>
-        </is>
-      </c>
-      <c r="C28">
-        <v>34.4631836811608</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>12101</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>Punta Arenas</t>
-        </is>
-      </c>
-      <c r="C29">
-        <v>33.9116318301039</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>12201</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>Cabo de Hornos</t>
-        </is>
-      </c>
-      <c r="C30">
-        <v>29.3172690763052</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>12302</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>Primavera</t>
-        </is>
-      </c>
-      <c r="C31">
-        <v>29.1666666666667</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>12201</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>Cabo de Hornos</t>
-        </is>
-      </c>
-      <c r="C32">
-        <v>20.6736353077816</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>12302</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>Primavera</t>
-        </is>
-      </c>
-      <c r="C33">
-        <v>19.7586726998492</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>12301</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>Porvenir</t>
-        </is>
-      </c>
-      <c r="C34">
-        <v>15.9178529062871</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>12101</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>Punta Arenas</t>
-        </is>
-      </c>
-      <c r="C35">
-        <v>13.3539550106892</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>12401</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>Natales</t>
-        </is>
-      </c>
-      <c r="C36">
-        <v>10.7304090020888</v>
       </c>
     </row>
   </sheetData>
